--- a/classifications/ifcreport.xlsx
+++ b/classifications/ifcreport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rmartin7\GitHub\iseapp\classifications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2C7DD1F-CEDA-469D-9F70-5ABCCA3AB02D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC78BC2C-1666-462E-A696-382200594421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{2AC61820-FA32-4A10-BE8B-0175A6EE5388}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
   <si>
     <t>Technology class</t>
   </si>
@@ -54,12 +54,6 @@
   </si>
   <si>
     <t>Espacenet</t>
-  </si>
-  <si>
-    <t>Non-green Technology</t>
-  </si>
-  <si>
-    <t>Not “Y02”</t>
   </si>
   <si>
     <t>Adaptation</t>
@@ -671,8 +665,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E02A3046-F897-4824-809A-DF33E1236110}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="38.1328125" customWidth="1"/>
+    <col min="2" max="2" width="32.46484375" customWidth="1"/>
+    <col min="3" max="3" width="33.06640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1"/>
@@ -688,7 +687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="47.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
@@ -699,16 +698,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="63.4" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="7"/>
-    </row>
-    <row r="5" spans="1:3" ht="32.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C4" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
@@ -730,7 +731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:3" ht="47.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
@@ -741,7 +742,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="47.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:3" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="4" t="s">
         <v>14</v>
       </c>
@@ -774,7 +775,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:3" ht="79.150000000000006" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A11" s="4" t="s">
         <v>20</v>
       </c>
@@ -785,18 +786,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="79.150000000000006" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:3" ht="47.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="47.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C12" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="79.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A13" s="6" t="s">
         <v>24</v>
       </c>
@@ -804,21 +805,21 @@
         <v>25</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="79.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="7" t="s">
+    </row>
+    <row r="14" spans="1:3" ht="32.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="B14" s="5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="32.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C14" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="157.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A15" s="4" t="s">
         <v>29</v>
       </c>
@@ -826,30 +827,28 @@
         <v>30</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="157.9" thickBot="1" x14ac:dyDescent="0.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="94.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A16" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="94.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C16" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A17" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="8" t="s">
         <v>36</v>
       </c>
+      <c r="C17" s="5"/>
     </row>
     <row r="18" spans="1:3" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A18" s="4" t="s">
@@ -860,7 +859,7 @@
       </c>
       <c r="C18" s="5"/>
     </row>
-    <row r="19" spans="1:3" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A19" s="4" t="s">
         <v>39</v>
       </c>
@@ -869,18 +868,9 @@
       </c>
       <c r="C19" s="5"/>
     </row>
-    <row r="20" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="5"/>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C17" r:id="rId1" display="https://www.aipla.org/docs/default-source/committee-documents/bcp-files/2019/cpcforbcp-approved.pdf" xr:uid="{754F93AD-240F-40A3-A9D9-957E62994ADF}"/>
+    <hyperlink ref="C16" r:id="rId1" display="https://www.aipla.org/docs/default-source/committee-documents/bcp-files/2019/cpcforbcp-approved.pdf" xr:uid="{754F93AD-240F-40A3-A9D9-957E62994ADF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>

--- a/classifications/ifcreport.xlsx
+++ b/classifications/ifcreport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rmartin7\GitHub\iseapp\classifications\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rmart\github\iseapp\classifications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC78BC2C-1666-462E-A696-382200594421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCF8FD26-C4C5-4D23-8B60-7BAA647BFBEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{2AC61820-FA32-4A10-BE8B-0175A6EE5388}"/>
+    <workbookView xWindow="3765" yWindow="3765" windowWidth="28800" windowHeight="15105" xr2:uid="{2AC61820-FA32-4A10-BE8B-0175A6EE5388}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -50,9 +50,6 @@
     <t>Green Technology</t>
   </si>
   <si>
-    <t>YO2</t>
-  </si>
-  <si>
     <t>Espacenet</t>
   </si>
   <si>
@@ -159,6 +156,9 @@
   </si>
   <si>
     <t>H04W</t>
+  </si>
+  <si>
+    <t>Y02</t>
   </si>
 </sst>
 </file>
@@ -666,17 +666,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E02A3046-F897-4824-809A-DF33E1236110}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.1328125" customWidth="1"/>
-    <col min="2" max="2" width="32.46484375" customWidth="1"/>
-    <col min="3" max="3" width="33.06640625" customWidth="1"/>
+    <col min="1" max="1" width="38.140625" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" customWidth="1"/>
+    <col min="3" max="3" width="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
     </row>
-    <row r="2" spans="1:3" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -687,184 +687,184 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="47.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="79.150000000000006" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="47.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="C12" s="7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="33" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="79.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="C13" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="7" t="s">
+    </row>
+    <row r="14" spans="1:3" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="32.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="157.9" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="5" t="s">
+    </row>
+    <row r="16" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="94.9" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="8" t="s">
+    </row>
+    <row r="17" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="5"/>
+    </row>
+    <row r="18" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="5"/>
-    </row>
-    <row r="18" spans="1:3" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="5"/>
+    </row>
+    <row r="19" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="5"/>
-    </row>
-    <row r="19" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>40</v>
       </c>
       <c r="C19" s="5"/>
     </row>
